--- a/data/nzd0520/nzd0520.xlsx
+++ b/data/nzd0520/nzd0520.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M368"/>
+  <dimension ref="A1:M369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16910,6 +16910,51 @@
       <c r="M368" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>266.81</v>
+      </c>
+      <c r="C369" t="n">
+        <v>246.16</v>
+      </c>
+      <c r="D369" t="n">
+        <v>237.71</v>
+      </c>
+      <c r="E369" t="n">
+        <v>242.99</v>
+      </c>
+      <c r="F369" t="n">
+        <v>264.42</v>
+      </c>
+      <c r="G369" t="n">
+        <v>288.29</v>
+      </c>
+      <c r="H369" t="n">
+        <v>290.27</v>
+      </c>
+      <c r="I369" t="n">
+        <v>297.07</v>
+      </c>
+      <c r="J369" t="n">
+        <v>311.21</v>
+      </c>
+      <c r="K369" t="n">
+        <v>327.91</v>
+      </c>
+      <c r="L369" t="n">
+        <v>331.35</v>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B399"/>
+  <dimension ref="A1:B400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20917,6 +20962,16 @@
       </c>
       <c r="B399" t="n">
         <v>-0.76</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -21085,28 +21140,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5214630604976012</v>
+        <v>-0.5273522234708757</v>
       </c>
       <c r="J2" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K2" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07033601297064573</v>
+        <v>0.07211627114783747</v>
       </c>
       <c r="M2" t="n">
-        <v>10.52443200208003</v>
+        <v>10.52839970048526</v>
       </c>
       <c r="N2" t="n">
-        <v>205.7478320065512</v>
+        <v>205.499718733583</v>
       </c>
       <c r="O2" t="n">
-        <v>14.34391271608104</v>
+        <v>14.33526137653524</v>
       </c>
       <c r="P2" t="n">
-        <v>291.329877637665</v>
+        <v>291.3881622473093</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21163,28 +21218,28 @@
         <v>0.1275</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7134774113536668</v>
+        <v>-0.7160086341072698</v>
       </c>
       <c r="J3" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09798583897248014</v>
+        <v>0.09915834821735647</v>
       </c>
       <c r="M3" t="n">
-        <v>12.87056052542603</v>
+        <v>12.8495373518844</v>
       </c>
       <c r="N3" t="n">
-        <v>267.2944006791301</v>
+        <v>266.5840682544857</v>
       </c>
       <c r="O3" t="n">
-        <v>16.34914067096892</v>
+        <v>16.32740237314208</v>
       </c>
       <c r="P3" t="n">
-        <v>269.3332989459648</v>
+        <v>269.3582729473349</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21241,28 +21296,28 @@
         <v>0.0459</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09468406588035444</v>
+        <v>-0.09813699674110213</v>
       </c>
       <c r="J4" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K4" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005651927903468246</v>
+        <v>0.006098511092599179</v>
       </c>
       <c r="M4" t="n">
-        <v>7.357943938072195</v>
+        <v>7.354534173071885</v>
       </c>
       <c r="N4" t="n">
-        <v>88.33984859004936</v>
+        <v>88.20796023722733</v>
       </c>
       <c r="O4" t="n">
-        <v>9.398928055371494</v>
+        <v>9.391909296688684</v>
       </c>
       <c r="P4" t="n">
-        <v>246.5495982921684</v>
+        <v>246.584032437973</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21319,28 +21374,28 @@
         <v>0.1024</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3611422173713899</v>
+        <v>0.3580445200143897</v>
       </c>
       <c r="J5" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K5" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06506634498347508</v>
+        <v>0.06434203527195148</v>
       </c>
       <c r="M5" t="n">
-        <v>8.278081231672981</v>
+        <v>8.267834967299791</v>
       </c>
       <c r="N5" t="n">
-        <v>104.964376992599</v>
+        <v>104.7656993401399</v>
       </c>
       <c r="O5" t="n">
-        <v>10.24521239372806</v>
+        <v>10.23551167944915</v>
       </c>
       <c r="P5" t="n">
-        <v>239.2464290954305</v>
+        <v>239.2773206964359</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21397,28 +21452,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3463024275157129</v>
+        <v>-0.3476564406282275</v>
       </c>
       <c r="J6" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K6" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07509841133910633</v>
+        <v>0.07605570719520605</v>
       </c>
       <c r="M6" t="n">
-        <v>7.064292655501856</v>
+        <v>7.05166351692691</v>
       </c>
       <c r="N6" t="n">
-        <v>82.72501932444885</v>
+        <v>82.51582895063945</v>
       </c>
       <c r="O6" t="n">
-        <v>9.095329533581994</v>
+        <v>9.083822375555318</v>
       </c>
       <c r="P6" t="n">
-        <v>275.9735168809931</v>
+        <v>275.9870196955058</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21475,28 +21530,28 @@
         <v>0.0809</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3127442861686988</v>
+        <v>-0.3108145787241084</v>
       </c>
       <c r="J7" t="n">
+        <v>368</v>
+      </c>
+      <c r="K7" t="n">
         <v>367</v>
       </c>
-      <c r="K7" t="n">
-        <v>366</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.09113649502118382</v>
+        <v>0.09056647901083015</v>
       </c>
       <c r="M7" t="n">
-        <v>5.712674836698369</v>
+        <v>5.706150717929505</v>
       </c>
       <c r="N7" t="n">
-        <v>54.48589289283913</v>
+        <v>54.37151482615528</v>
       </c>
       <c r="O7" t="n">
-        <v>7.381456014421485</v>
+        <v>7.373704281170712</v>
       </c>
       <c r="P7" t="n">
-        <v>292.919241311743</v>
+        <v>292.89997488604</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21553,28 +21608,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.274618616441879</v>
+        <v>-0.2773894742036415</v>
       </c>
       <c r="J8" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K8" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02260378328909873</v>
+        <v>0.02318065857592511</v>
       </c>
       <c r="M8" t="n">
-        <v>9.74304234387421</v>
+        <v>9.733374195323579</v>
       </c>
       <c r="N8" t="n">
-        <v>182.6218698297579</v>
+        <v>182.1934123588809</v>
       </c>
       <c r="O8" t="n">
-        <v>13.51376593810022</v>
+        <v>13.49790399872813</v>
       </c>
       <c r="P8" t="n">
-        <v>302.5586569891707</v>
+        <v>302.5862947245939</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21635,28 +21690,28 @@
         <v>0.1729</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4596480572002097</v>
+        <v>-0.4638922442087245</v>
       </c>
       <c r="J9" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K9" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04602429739992309</v>
+        <v>0.04707933468151593</v>
       </c>
       <c r="M9" t="n">
-        <v>11.32386819487914</v>
+        <v>11.31941300078776</v>
       </c>
       <c r="N9" t="n">
-        <v>247.1056396962118</v>
+        <v>246.5980276630567</v>
       </c>
       <c r="O9" t="n">
-        <v>15.71959413268077</v>
+        <v>15.70343999456988</v>
       </c>
       <c r="P9" t="n">
-        <v>316.9647449625942</v>
+        <v>317.006886388101</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -21717,28 +21772,28 @@
         <v>0.1334</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5346886817554035</v>
+        <v>-0.5354526513344942</v>
       </c>
       <c r="J10" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K10" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07619524125242794</v>
+        <v>0.07682482855709971</v>
       </c>
       <c r="M10" t="n">
-        <v>10.64938318089164</v>
+        <v>10.6246808274707</v>
       </c>
       <c r="N10" t="n">
-        <v>195.204529954456</v>
+        <v>194.6794882007885</v>
       </c>
       <c r="O10" t="n">
-        <v>13.97156147159136</v>
+        <v>13.95275916085376</v>
       </c>
       <c r="P10" t="n">
-        <v>326.6252127922997</v>
+        <v>326.6327919779086</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21795,28 +21850,28 @@
         <v>0.1563</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07087035274015235</v>
+        <v>-0.06702885388185213</v>
       </c>
       <c r="J11" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K11" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0007483931469235428</v>
+        <v>0.0006733501752149706</v>
       </c>
       <c r="M11" t="n">
-        <v>15.01033721595745</v>
+        <v>14.98392481151561</v>
       </c>
       <c r="N11" t="n">
-        <v>377.66766662263</v>
+        <v>376.7780654733267</v>
       </c>
       <c r="O11" t="n">
-        <v>19.43367352361951</v>
+        <v>19.41077189277456</v>
       </c>
       <c r="P11" t="n">
-        <v>322.6384725738534</v>
+        <v>322.6003618510442</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21873,28 +21928,28 @@
         <v>0.1938</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5054962347687612</v>
+        <v>0.5100007076813908</v>
       </c>
       <c r="J12" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K12" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02370867644355623</v>
+        <v>0.02426249929768254</v>
       </c>
       <c r="M12" t="n">
-        <v>18.84198227471096</v>
+        <v>18.8061957842991</v>
       </c>
       <c r="N12" t="n">
-        <v>580.8278327997514</v>
+        <v>579.3943797722022</v>
       </c>
       <c r="O12" t="n">
-        <v>24.10036997225875</v>
+        <v>24.07061236803506</v>
       </c>
       <c r="P12" t="n">
-        <v>310.0377365526124</v>
+        <v>309.9923379620901</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21932,7 +21987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M368"/>
+  <dimension ref="A1:M369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46391,6 +46446,73 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>-46.22056948802579,166.7783041121245</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>-46.22002878351289,166.7778116775713</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>-46.219566724335024,166.7772094994158</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-46.21919317243354,166.77648381643797</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>-46.21892372634773,166.7756128605973</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>-46.2186700043036,166.7747199562667</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-46.2182751678643,166.77402395858815</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-46.217911399173296,166.77328460389157</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>-46.217594942032974,166.772479224241</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>-46.21729498278606,166.7716508169058</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>-46.21690954371886,166.7709416870521</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0520/nzd0520.xlsx
+++ b/data/nzd0520/nzd0520.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M369"/>
+  <dimension ref="A1:M370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16955,6 +16955,51 @@
       <c r="M369" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>269.32</v>
+      </c>
+      <c r="C370" t="n">
+        <v>248.94</v>
+      </c>
+      <c r="D370" t="n">
+        <v>238.99</v>
+      </c>
+      <c r="E370" t="n">
+        <v>245.09</v>
+      </c>
+      <c r="F370" t="n">
+        <v>263.91</v>
+      </c>
+      <c r="G370" t="n">
+        <v>288.29</v>
+      </c>
+      <c r="H370" t="n">
+        <v>292.32</v>
+      </c>
+      <c r="I370" t="n">
+        <v>299.32</v>
+      </c>
+      <c r="J370" t="n">
+        <v>312.83</v>
+      </c>
+      <c r="K370" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="L370" t="n">
+        <v>328.86</v>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16969,7 +17014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B400"/>
+  <dimension ref="A1:B401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20972,6 +21017,16 @@
       </c>
       <c r="B400" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -21140,28 +21195,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5273522234708757</v>
+        <v>-0.5317924549875445</v>
       </c>
       <c r="J2" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K2" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07211627114783747</v>
+        <v>0.07359233996124181</v>
       </c>
       <c r="M2" t="n">
-        <v>10.52839970048526</v>
+        <v>10.52427969451411</v>
       </c>
       <c r="N2" t="n">
-        <v>205.499718733583</v>
+        <v>205.1143222940483</v>
       </c>
       <c r="O2" t="n">
-        <v>14.33526137653524</v>
+        <v>14.32181281451647</v>
       </c>
       <c r="P2" t="n">
-        <v>291.3881622473093</v>
+        <v>291.4321520881939</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21218,28 +21273,28 @@
         <v>0.1275</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7160086341072698</v>
+        <v>-0.7169340821313372</v>
       </c>
       <c r="J3" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K3" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09915834821735647</v>
+        <v>0.09995009323259496</v>
       </c>
       <c r="M3" t="n">
-        <v>12.8495373518844</v>
+        <v>12.81854876355558</v>
       </c>
       <c r="N3" t="n">
-        <v>266.5840682544857</v>
+        <v>265.8280272157106</v>
       </c>
       <c r="O3" t="n">
-        <v>16.32740237314208</v>
+        <v>16.30423341392384</v>
       </c>
       <c r="P3" t="n">
-        <v>269.3582729473349</v>
+        <v>269.3674130076863</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21296,28 +21351,28 @@
         <v>0.0459</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09813699674110213</v>
+        <v>-0.1008464876537121</v>
       </c>
       <c r="J4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K4" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006098511092599179</v>
+        <v>0.006471578844919335</v>
       </c>
       <c r="M4" t="n">
-        <v>7.354534173071885</v>
+        <v>7.347533465643489</v>
       </c>
       <c r="N4" t="n">
-        <v>88.20796023722733</v>
+        <v>88.03576542402</v>
       </c>
       <c r="O4" t="n">
-        <v>9.391909296688684</v>
+        <v>9.382737629499186</v>
       </c>
       <c r="P4" t="n">
-        <v>246.584032437973</v>
+        <v>246.6110793494386</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21374,28 +21429,28 @@
         <v>0.1024</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3580445200143897</v>
+        <v>0.3561213519875846</v>
       </c>
       <c r="J5" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K5" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06434203527195148</v>
+        <v>0.06403899190868223</v>
       </c>
       <c r="M5" t="n">
-        <v>8.267834967299791</v>
+        <v>8.252949308312843</v>
       </c>
       <c r="N5" t="n">
-        <v>104.7656993401399</v>
+        <v>104.5145702012245</v>
       </c>
       <c r="O5" t="n">
-        <v>10.23551167944915</v>
+        <v>10.2232367771281</v>
       </c>
       <c r="P5" t="n">
-        <v>239.2773206964359</v>
+        <v>239.2965183084716</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21452,28 +21507,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3476564406282275</v>
+        <v>-0.3492607672721695</v>
       </c>
       <c r="J6" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K6" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07605570719520605</v>
+        <v>0.07711459019006328</v>
       </c>
       <c r="M6" t="n">
-        <v>7.05166351692691</v>
+        <v>7.0403164467137</v>
       </c>
       <c r="N6" t="n">
-        <v>82.51582895063945</v>
+        <v>82.31488482579911</v>
       </c>
       <c r="O6" t="n">
-        <v>9.083822375555318</v>
+        <v>9.07275508463659</v>
       </c>
       <c r="P6" t="n">
-        <v>275.9870196955058</v>
+        <v>276.0030345418737</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21530,28 +21585,28 @@
         <v>0.0809</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3108145787241084</v>
+        <v>-0.3089111714124051</v>
       </c>
       <c r="J7" t="n">
+        <v>369</v>
+      </c>
+      <c r="K7" t="n">
         <v>368</v>
       </c>
-      <c r="K7" t="n">
-        <v>367</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.09056647901083015</v>
+        <v>0.09000424781207128</v>
       </c>
       <c r="M7" t="n">
-        <v>5.706150717929505</v>
+        <v>5.699521699202377</v>
       </c>
       <c r="N7" t="n">
-        <v>54.37151482615528</v>
+        <v>54.25729419606314</v>
       </c>
       <c r="O7" t="n">
-        <v>7.373704281170712</v>
+        <v>7.36595507697835</v>
       </c>
       <c r="P7" t="n">
-        <v>292.89997488604</v>
+        <v>292.8809523644853</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21608,28 +21663,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2773894742036415</v>
+        <v>-0.279007444485088</v>
       </c>
       <c r="J8" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K8" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02318065857592511</v>
+        <v>0.02358142839563915</v>
       </c>
       <c r="M8" t="n">
-        <v>9.733374195323579</v>
+        <v>9.716705538444835</v>
       </c>
       <c r="N8" t="n">
-        <v>182.1934123588809</v>
+        <v>181.7212791380989</v>
       </c>
       <c r="O8" t="n">
-        <v>13.49790399872813</v>
+        <v>13.48040352282152</v>
       </c>
       <c r="P8" t="n">
-        <v>302.5862947245939</v>
+        <v>302.6024489951395</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21690,28 +21745,28 @@
         <v>0.1729</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4638922442087245</v>
+        <v>-0.466858120856507</v>
       </c>
       <c r="J9" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K9" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04707933468151593</v>
+        <v>0.04791320814134759</v>
       </c>
       <c r="M9" t="n">
-        <v>11.31941300078776</v>
+        <v>11.30699242148825</v>
       </c>
       <c r="N9" t="n">
-        <v>246.5980276630567</v>
+        <v>246.0088116923051</v>
       </c>
       <c r="O9" t="n">
-        <v>15.70343999456988</v>
+        <v>15.68466804533348</v>
       </c>
       <c r="P9" t="n">
-        <v>317.006886388101</v>
+        <v>317.0363645604911</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -21772,28 +21827,28 @@
         <v>0.1334</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5354526513344942</v>
+        <v>-0.5353345623034759</v>
       </c>
       <c r="J10" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K10" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07682482855709971</v>
+        <v>0.07722258124572912</v>
       </c>
       <c r="M10" t="n">
-        <v>10.6246808274707</v>
+        <v>10.59642036595044</v>
       </c>
       <c r="N10" t="n">
-        <v>194.6794882007885</v>
+        <v>194.1520320809691</v>
       </c>
       <c r="O10" t="n">
-        <v>13.95275916085376</v>
+        <v>13.9338448420014</v>
       </c>
       <c r="P10" t="n">
-        <v>326.6327919779086</v>
+        <v>326.6316192809564</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21850,28 +21905,28 @@
         <v>0.1563</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06702885388185213</v>
+        <v>-0.06346157585867378</v>
       </c>
       <c r="J11" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K11" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0006733501752149706</v>
+        <v>0.0006070884133192456</v>
       </c>
       <c r="M11" t="n">
-        <v>14.98392481151561</v>
+        <v>14.95674583882237</v>
       </c>
       <c r="N11" t="n">
-        <v>376.7780654733267</v>
+        <v>375.87613699812</v>
       </c>
       <c r="O11" t="n">
-        <v>19.41077189277456</v>
+        <v>19.38752529329414</v>
       </c>
       <c r="P11" t="n">
-        <v>322.6003618510442</v>
+        <v>322.5649365788614</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21928,28 +21983,28 @@
         <v>0.1938</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5100007076813908</v>
+        <v>0.51304850384092</v>
       </c>
       <c r="J12" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K12" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02426249929768254</v>
+        <v>0.02469108707971257</v>
       </c>
       <c r="M12" t="n">
-        <v>18.8061957842991</v>
+        <v>18.76524791026369</v>
       </c>
       <c r="N12" t="n">
-        <v>579.3943797722022</v>
+        <v>577.8727270393407</v>
       </c>
       <c r="O12" t="n">
-        <v>24.07061236803506</v>
+        <v>24.03898348598253</v>
       </c>
       <c r="P12" t="n">
-        <v>309.9923379620901</v>
+        <v>309.9615906713227</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21987,7 +22042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M369"/>
+  <dimension ref="A1:M370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46513,6 +46568,73 @@
         </is>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>-46.22058566882579,166.77828153379767</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>-46.22004670481976,166.77778667068355</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>-46.21957497583376,166.7771979855068</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>-46.21920670996025,166.77646492645277</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>-46.21892043869017,166.77561744817544</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>-46.2186700043036,166.7747199562667</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-46.21828838275932,166.77400551829695</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>-46.217925903229414,166.77326436456516</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>-46.21760538487439,166.77246465191485</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>-46.21729233986534,166.7716545049681</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>-46.216893492908156,166.77096408524088</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0520/nzd0520.xlsx
+++ b/data/nzd0520/nzd0520.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M370"/>
+  <dimension ref="A1:M371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17000,6 +17000,51 @@
       <c r="M370" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:27:11+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>273.86</v>
+      </c>
+      <c r="C371" t="n">
+        <v>252.97</v>
+      </c>
+      <c r="D371" t="n">
+        <v>241.62</v>
+      </c>
+      <c r="E371" t="n">
+        <v>247.72</v>
+      </c>
+      <c r="F371" t="n">
+        <v>265.98</v>
+      </c>
+      <c r="G371" t="n">
+        <v>290.29</v>
+      </c>
+      <c r="H371" t="n">
+        <v>296.15</v>
+      </c>
+      <c r="I371" t="n">
+        <v>302.91</v>
+      </c>
+      <c r="J371" t="n">
+        <v>315.44</v>
+      </c>
+      <c r="K371" t="n">
+        <v>328.63</v>
+      </c>
+      <c r="L371" t="n">
+        <v>327.77</v>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -17014,7 +17059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B401"/>
+  <dimension ref="A1:B402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21027,6 +21072,16 @@
       </c>
       <c r="B401" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -21195,28 +21250,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5317924549875445</v>
+        <v>-0.5337276194231468</v>
       </c>
       <c r="J2" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07359233996124181</v>
+        <v>0.07449007249882533</v>
       </c>
       <c r="M2" t="n">
-        <v>10.52427969451411</v>
+        <v>10.50589338097974</v>
       </c>
       <c r="N2" t="n">
-        <v>205.1143222940483</v>
+        <v>204.578908916724</v>
       </c>
       <c r="O2" t="n">
-        <v>14.32181281451647</v>
+        <v>14.30310836555202</v>
       </c>
       <c r="P2" t="n">
-        <v>291.4321520881939</v>
+        <v>291.4513831166468</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21273,28 +21328,28 @@
         <v>0.1275</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7169340821313372</v>
+        <v>-0.71558521639003</v>
       </c>
       <c r="J3" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09995009323259496</v>
+        <v>0.1001704573932641</v>
       </c>
       <c r="M3" t="n">
-        <v>12.81854876355558</v>
+        <v>12.7872289572274</v>
       </c>
       <c r="N3" t="n">
-        <v>265.8280272157106</v>
+        <v>265.0851720009064</v>
       </c>
       <c r="O3" t="n">
-        <v>16.30423341392384</v>
+        <v>16.28143642314481</v>
       </c>
       <c r="P3" t="n">
-        <v>269.3674130076863</v>
+        <v>269.3540506637273</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21351,28 +21406,28 @@
         <v>0.0459</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1008464876537121</v>
+        <v>-0.1021051016847209</v>
       </c>
       <c r="J4" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K4" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006471578844919335</v>
+        <v>0.006671959745542022</v>
       </c>
       <c r="M4" t="n">
-        <v>7.347533465643489</v>
+        <v>7.333572933895148</v>
       </c>
       <c r="N4" t="n">
-        <v>88.03576542402</v>
+        <v>87.81128966920737</v>
       </c>
       <c r="O4" t="n">
-        <v>9.382737629499186</v>
+        <v>9.370767827089058</v>
       </c>
       <c r="P4" t="n">
-        <v>246.6110793494386</v>
+        <v>246.6236804039333</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21429,28 +21484,28 @@
         <v>0.1024</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3561213519875846</v>
+        <v>0.3556218295260358</v>
       </c>
       <c r="J5" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K5" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06403899190868223</v>
+        <v>0.06423269142034382</v>
       </c>
       <c r="M5" t="n">
-        <v>8.252949308312843</v>
+        <v>8.23248907645079</v>
       </c>
       <c r="N5" t="n">
-        <v>104.5145702012245</v>
+        <v>104.2328868735529</v>
       </c>
       <c r="O5" t="n">
-        <v>10.2232367771281</v>
+        <v>10.20945086052883</v>
       </c>
       <c r="P5" t="n">
-        <v>239.2965183084716</v>
+        <v>239.3015194522728</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21507,28 +21562,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3492607672721695</v>
+        <v>-0.349721108588635</v>
       </c>
       <c r="J6" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K6" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07711459019006328</v>
+        <v>0.07773367118590835</v>
       </c>
       <c r="M6" t="n">
-        <v>7.0403164467137</v>
+        <v>7.023421934988515</v>
       </c>
       <c r="N6" t="n">
-        <v>82.31488482579911</v>
+        <v>82.0931765039311</v>
       </c>
       <c r="O6" t="n">
-        <v>9.07275508463659</v>
+        <v>9.060528489218004</v>
       </c>
       <c r="P6" t="n">
-        <v>276.0030345418737</v>
+        <v>276.0076434099397</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21585,28 +21640,28 @@
         <v>0.0809</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3089111714124051</v>
+        <v>-0.305939454092262</v>
       </c>
       <c r="J7" t="n">
+        <v>370</v>
+      </c>
+      <c r="K7" t="n">
         <v>369</v>
       </c>
-      <c r="K7" t="n">
-        <v>368</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.09000424781207128</v>
+        <v>0.08880044550612765</v>
       </c>
       <c r="M7" t="n">
-        <v>5.699521699202377</v>
+        <v>5.697815691335295</v>
       </c>
       <c r="N7" t="n">
-        <v>54.25729419606314</v>
+        <v>54.19223539862239</v>
       </c>
       <c r="O7" t="n">
-        <v>7.36595507697835</v>
+        <v>7.361537570278535</v>
       </c>
       <c r="P7" t="n">
-        <v>292.8809523644853</v>
+        <v>292.851165652248</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21663,28 +21718,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.279007444485088</v>
+        <v>-0.2785363764290469</v>
       </c>
       <c r="J8" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K8" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02358142839563915</v>
+        <v>0.02364284557817298</v>
       </c>
       <c r="M8" t="n">
-        <v>9.716705538444835</v>
+        <v>9.69217618040771</v>
       </c>
       <c r="N8" t="n">
-        <v>181.7212791380989</v>
+        <v>181.2295380961433</v>
       </c>
       <c r="O8" t="n">
-        <v>13.48040352282152</v>
+        <v>13.46215206035585</v>
       </c>
       <c r="P8" t="n">
-        <v>302.6024489951395</v>
+        <v>302.5977317882692</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21745,28 +21800,28 @@
         <v>0.1729</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.466858120856507</v>
+        <v>-0.4678580092807226</v>
       </c>
       <c r="J9" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K9" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04791320814134759</v>
+        <v>0.04838363150765879</v>
       </c>
       <c r="M9" t="n">
-        <v>11.30699242148825</v>
+        <v>11.28242592624144</v>
       </c>
       <c r="N9" t="n">
-        <v>246.0088116923051</v>
+        <v>245.3497391347285</v>
       </c>
       <c r="O9" t="n">
-        <v>15.68466804533348</v>
+        <v>15.66364386516523</v>
       </c>
       <c r="P9" t="n">
-        <v>317.0363645604911</v>
+        <v>317.0463322823371</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -21827,28 +21882,28 @@
         <v>0.1334</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5353345623034759</v>
+        <v>-0.5338022202503008</v>
       </c>
       <c r="J10" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K10" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07722258124572912</v>
+        <v>0.0772362151114252</v>
       </c>
       <c r="M10" t="n">
-        <v>10.59642036595044</v>
+        <v>10.57463323852</v>
       </c>
       <c r="N10" t="n">
-        <v>194.1520320809691</v>
+        <v>193.6493503288467</v>
       </c>
       <c r="O10" t="n">
-        <v>13.9338448420014</v>
+        <v>13.91579499449624</v>
       </c>
       <c r="P10" t="n">
-        <v>326.6316192809564</v>
+        <v>326.6163569833703</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21905,28 +21960,28 @@
         <v>0.1563</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06346157585867378</v>
+        <v>-0.05933147800282997</v>
       </c>
       <c r="J11" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K11" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0006070884133192456</v>
+        <v>0.0005336656767932491</v>
       </c>
       <c r="M11" t="n">
-        <v>14.95674583882237</v>
+        <v>14.93189974300125</v>
       </c>
       <c r="N11" t="n">
-        <v>375.87613699812</v>
+        <v>375.0204642739868</v>
       </c>
       <c r="O11" t="n">
-        <v>19.38752529329414</v>
+        <v>19.36544510911089</v>
       </c>
       <c r="P11" t="n">
-        <v>322.5649365788614</v>
+        <v>322.523800344034</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21983,28 +22038,28 @@
         <v>0.1938</v>
       </c>
       <c r="I12" t="n">
-        <v>0.51304850384092</v>
+        <v>0.5154373431361735</v>
       </c>
       <c r="J12" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K12" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02469108707971257</v>
+        <v>0.02506416818391499</v>
       </c>
       <c r="M12" t="n">
-        <v>18.76524791026369</v>
+        <v>18.72212161411832</v>
       </c>
       <c r="N12" t="n">
-        <v>577.8727270393407</v>
+        <v>576.3277487148606</v>
       </c>
       <c r="O12" t="n">
-        <v>24.03898348598253</v>
+        <v>24.00682712719156</v>
       </c>
       <c r="P12" t="n">
-        <v>309.9615906713227</v>
+        <v>309.9374207955863</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22042,7 +22097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M370"/>
+  <dimension ref="A1:M371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46635,6 +46690,73 @@
         </is>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:27:11+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>-46.220614936076394,166.7782406948777</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>-46.220072684256934,166.77775041966245</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>-46.21959193008081,166.777174328011</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>-46.219223664095736,166.77644126898196</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>-46.21893378271068,166.77559882800182</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>-46.21868289696225,166.77470196570232</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-46.218313072041745,166.77397106641197</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>-46.217949045248155,166.7732320715732</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>-46.21762220944769,166.77244117426648</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>-46.21729962401236,166.77164434030772</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>-46.216886466648056,166.7709738900664</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0520/nzd0520.xlsx
+++ b/data/nzd0520/nzd0520.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M371"/>
+  <dimension ref="A1:M373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17043,6 +17043,96 @@
         <v>327.77</v>
       </c>
       <c r="M371" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:33:16+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>285.25</v>
+      </c>
+      <c r="C372" t="n">
+        <v>265.39</v>
+      </c>
+      <c r="D372" t="n">
+        <v>250.68</v>
+      </c>
+      <c r="E372" t="n">
+        <v>255.37</v>
+      </c>
+      <c r="F372" t="n">
+        <v>264.22</v>
+      </c>
+      <c r="G372" t="n">
+        <v>289.35</v>
+      </c>
+      <c r="H372" t="n">
+        <v>298.24</v>
+      </c>
+      <c r="I372" t="n">
+        <v>310.04</v>
+      </c>
+      <c r="J372" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="K372" t="n">
+        <v>326.66</v>
+      </c>
+      <c r="L372" t="n">
+        <v>322.43</v>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-10 22:32:58+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>288.36</v>
+      </c>
+      <c r="C373" t="n">
+        <v>274.09</v>
+      </c>
+      <c r="D373" t="n">
+        <v>251.72</v>
+      </c>
+      <c r="E373" t="n">
+        <v>259.28</v>
+      </c>
+      <c r="F373" t="n">
+        <v>266.21</v>
+      </c>
+      <c r="G373" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="H373" t="n">
+        <v>302.87</v>
+      </c>
+      <c r="I373" t="n">
+        <v>312.99</v>
+      </c>
+      <c r="J373" t="n">
+        <v>321.44</v>
+      </c>
+      <c r="K373" t="n">
+        <v>326.82</v>
+      </c>
+      <c r="L373" t="n">
+        <v>323.13</v>
+      </c>
+      <c r="M373" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17059,7 +17149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B402"/>
+  <dimension ref="A1:B404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21082,6 +21172,26 @@
       </c>
       <c r="B402" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-03-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>-0.44</v>
       </c>
     </row>
   </sheetData>
@@ -21250,28 +21360,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5337276194231468</v>
+        <v>-0.523585079164489</v>
       </c>
       <c r="J2" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07449007249882533</v>
+        <v>0.07253966930838818</v>
       </c>
       <c r="M2" t="n">
-        <v>10.50589338097974</v>
+        <v>10.49478879948085</v>
       </c>
       <c r="N2" t="n">
-        <v>204.578908916724</v>
+        <v>203.9467175982643</v>
       </c>
       <c r="O2" t="n">
-        <v>14.30310836555202</v>
+        <v>14.28099147812449</v>
       </c>
       <c r="P2" t="n">
-        <v>291.4513831166468</v>
+        <v>291.3497275513978</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21328,28 +21438,28 @@
         <v>0.1275</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.71558521639003</v>
+        <v>-0.6941496987142952</v>
       </c>
       <c r="J3" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K3" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1001704573932641</v>
+        <v>0.09520386411021153</v>
       </c>
       <c r="M3" t="n">
-        <v>12.7872289572274</v>
+        <v>12.79869788467499</v>
       </c>
       <c r="N3" t="n">
-        <v>265.0851720009064</v>
+        <v>265.7666537330449</v>
       </c>
       <c r="O3" t="n">
-        <v>16.28143642314481</v>
+        <v>16.3023511719336</v>
       </c>
       <c r="P3" t="n">
-        <v>269.3540506637273</v>
+        <v>269.1399071519007</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21406,28 +21516,28 @@
         <v>0.0459</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1021051016847209</v>
+        <v>-0.09428683562904674</v>
       </c>
       <c r="J4" t="n">
+        <v>372</v>
+      </c>
+      <c r="K4" t="n">
         <v>370</v>
       </c>
-      <c r="K4" t="n">
-        <v>368</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.006671959745542022</v>
+        <v>0.005746484865563284</v>
       </c>
       <c r="M4" t="n">
-        <v>7.333572933895148</v>
+        <v>7.334728365432973</v>
       </c>
       <c r="N4" t="n">
-        <v>87.81128966920737</v>
+        <v>87.61945352780046</v>
       </c>
       <c r="O4" t="n">
-        <v>9.370767827089058</v>
+        <v>9.360526348865243</v>
       </c>
       <c r="P4" t="n">
-        <v>246.6236804039333</v>
+        <v>246.5447656441248</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21484,28 +21594,28 @@
         <v>0.1024</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3556218295260358</v>
+        <v>0.364885365962921</v>
       </c>
       <c r="J5" t="n">
+        <v>372</v>
+      </c>
+      <c r="K5" t="n">
         <v>370</v>
       </c>
-      <c r="K5" t="n">
-        <v>368</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.06423269142034382</v>
+        <v>0.0679177048065549</v>
       </c>
       <c r="M5" t="n">
-        <v>8.23248907645079</v>
+        <v>8.243995102659092</v>
       </c>
       <c r="N5" t="n">
-        <v>104.2328868735529</v>
+        <v>104.0848931630465</v>
       </c>
       <c r="O5" t="n">
-        <v>10.20945086052883</v>
+        <v>10.20220040790449</v>
       </c>
       <c r="P5" t="n">
-        <v>239.3015194522728</v>
+        <v>239.2080096925494</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21562,28 +21672,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.349721108588635</v>
+        <v>-0.3513751097700155</v>
       </c>
       <c r="J6" t="n">
+        <v>372</v>
+      </c>
+      <c r="K6" t="n">
         <v>370</v>
       </c>
-      <c r="K6" t="n">
-        <v>368</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.07773367118590835</v>
+        <v>0.07929017353938239</v>
       </c>
       <c r="M6" t="n">
-        <v>7.023421934988515</v>
+        <v>6.993343237149197</v>
       </c>
       <c r="N6" t="n">
-        <v>82.0931765039311</v>
+        <v>81.66744142119954</v>
       </c>
       <c r="O6" t="n">
-        <v>9.060528489218004</v>
+        <v>9.037004006926164</v>
       </c>
       <c r="P6" t="n">
-        <v>276.0076434099397</v>
+        <v>276.0243324943789</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21640,28 +21750,28 @@
         <v>0.0809</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.305939454092262</v>
+        <v>-0.2991502382803918</v>
       </c>
       <c r="J7" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K7" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08880044550612765</v>
+        <v>0.08586832568145764</v>
       </c>
       <c r="M7" t="n">
-        <v>5.697815691335295</v>
+        <v>5.69780130967524</v>
       </c>
       <c r="N7" t="n">
-        <v>54.19223539862239</v>
+        <v>54.12758817361141</v>
       </c>
       <c r="O7" t="n">
-        <v>7.361537570278535</v>
+        <v>7.357145382117402</v>
       </c>
       <c r="P7" t="n">
-        <v>292.851165652248</v>
+        <v>292.7825544818798</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21718,28 +21828,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2785363764290469</v>
+        <v>-0.27281493929818</v>
       </c>
       <c r="J8" t="n">
+        <v>372</v>
+      </c>
+      <c r="K8" t="n">
         <v>370</v>
       </c>
-      <c r="K8" t="n">
-        <v>368</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.02364284557817298</v>
+        <v>0.02295540889023395</v>
       </c>
       <c r="M8" t="n">
-        <v>9.69217618040771</v>
+        <v>9.662050276463598</v>
       </c>
       <c r="N8" t="n">
-        <v>181.2295380961433</v>
+        <v>180.4295610722654</v>
       </c>
       <c r="O8" t="n">
-        <v>13.46215206035585</v>
+        <v>13.43240712129682</v>
       </c>
       <c r="P8" t="n">
-        <v>302.5977317882692</v>
+        <v>302.5399599362877</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21800,28 +21910,28 @@
         <v>0.1729</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4678580092807226</v>
+        <v>-0.4605548082075787</v>
       </c>
       <c r="J9" t="n">
+        <v>372</v>
+      </c>
+      <c r="K9" t="n">
         <v>370</v>
       </c>
-      <c r="K9" t="n">
-        <v>368</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.04838363150765879</v>
+        <v>0.04745749774383123</v>
       </c>
       <c r="M9" t="n">
-        <v>11.28242592624144</v>
+        <v>11.25006842254031</v>
       </c>
       <c r="N9" t="n">
-        <v>245.3497391347285</v>
+        <v>244.2839168799159</v>
       </c>
       <c r="O9" t="n">
-        <v>15.66364386516523</v>
+        <v>15.62958466754366</v>
       </c>
       <c r="P9" t="n">
-        <v>317.0463322823371</v>
+        <v>316.972922156354</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -21882,28 +21992,28 @@
         <v>0.1334</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5338022202503008</v>
+        <v>-0.5243185565234287</v>
       </c>
       <c r="J10" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K10" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0772362151114252</v>
+        <v>0.07542034871761316</v>
       </c>
       <c r="M10" t="n">
-        <v>10.57463323852</v>
+        <v>10.55965895809293</v>
       </c>
       <c r="N10" t="n">
-        <v>193.6493503288467</v>
+        <v>193.0258238745831</v>
       </c>
       <c r="O10" t="n">
-        <v>13.91579499449624</v>
+        <v>13.89337337994567</v>
       </c>
       <c r="P10" t="n">
-        <v>326.6163569833703</v>
+        <v>326.5211278191758</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21960,28 +22070,28 @@
         <v>0.1563</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.05933147800282997</v>
+        <v>-0.05315674314863816</v>
       </c>
       <c r="J11" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K11" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0005336656767932491</v>
+        <v>0.000433488656697234</v>
       </c>
       <c r="M11" t="n">
-        <v>14.93189974300125</v>
+        <v>14.87438258164388</v>
       </c>
       <c r="N11" t="n">
-        <v>375.0204642739868</v>
+        <v>373.1812814933402</v>
       </c>
       <c r="O11" t="n">
-        <v>19.36544510911089</v>
+        <v>19.3179005456944</v>
       </c>
       <c r="P11" t="n">
-        <v>322.523800344034</v>
+        <v>322.461797167414</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22038,28 +22148,28 @@
         <v>0.1938</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5154373431361735</v>
+        <v>0.5145725610607494</v>
       </c>
       <c r="J12" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K12" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02506416818391499</v>
+        <v>0.0252894160287459</v>
       </c>
       <c r="M12" t="n">
-        <v>18.72212161411832</v>
+        <v>18.62461289487549</v>
       </c>
       <c r="N12" t="n">
-        <v>576.3277487148606</v>
+        <v>573.1650900362072</v>
       </c>
       <c r="O12" t="n">
-        <v>24.00682712719156</v>
+        <v>23.9408665264273</v>
       </c>
       <c r="P12" t="n">
-        <v>309.9374207955863</v>
+        <v>309.946238873393</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22097,7 +22207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M371"/>
+  <dimension ref="A1:M373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46757,6 +46867,140 @@
         </is>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:33:16+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>-46.22068836198975,166.77813823757091</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>-46.22015274983316,166.7776386979365</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>-46.219650335162285,166.7770928309739</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-46.219272979324494,166.77637245534265</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>-46.21892243707028,166.77561465964763</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-46.21867683741309,166.77471042126862</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-46.21832654477826,166.77395226628403</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>-46.217995006942026,166.7731679352713</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>-46.21766030644933,166.77238801218175</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>-46.217286925100495,166.77166206099707</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>-46.216852044405606,166.77102192467962</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-10 22:32:58+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>-46.220708410662255,166.77811026191077</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>-46.2202088343402,166.7775604385615</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>-46.219657039494045,166.7770834758945</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-46.219298184867334,166.77633728387906</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>-46.2189352653794,166.77559675909308</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>-46.21869907724421,166.77467938753202</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-46.218356391066976,166.77391061812077</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-46.21801402333893,166.77314139918215</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>-46.21766088660649,166.7723872026063</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>-46.21728795648431,166.77166062175357</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>-46.21685655668591,166.7710156280109</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0520/nzd0520.xlsx
+++ b/data/nzd0520/nzd0520.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M373"/>
+  <dimension ref="A1:M374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17133,6 +17133,51 @@
         <v>323.13</v>
       </c>
       <c r="M373" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>289.14</v>
+      </c>
+      <c r="C374" t="n">
+        <v>274.71</v>
+      </c>
+      <c r="D374" t="n">
+        <v>251.93</v>
+      </c>
+      <c r="E374" t="n">
+        <v>260.89</v>
+      </c>
+      <c r="F374" t="n">
+        <v>266.68</v>
+      </c>
+      <c r="G374" t="n">
+        <v>293.94</v>
+      </c>
+      <c r="H374" t="n">
+        <v>304.02</v>
+      </c>
+      <c r="I374" t="n">
+        <v>314.38</v>
+      </c>
+      <c r="J374" t="n">
+        <v>324.46</v>
+      </c>
+      <c r="K374" t="n">
+        <v>327.47</v>
+      </c>
+      <c r="L374" t="n">
+        <v>323.01</v>
+      </c>
+      <c r="M374" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17149,7 +17194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B404"/>
+  <dimension ref="A1:B405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21192,6 +21237,16 @@
       </c>
       <c r="B404" t="n">
         <v>-0.44</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -21360,28 +21415,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.523585079164489</v>
+        <v>-0.5173794221230359</v>
       </c>
       <c r="J2" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07253966930838818</v>
+        <v>0.07122927031148285</v>
       </c>
       <c r="M2" t="n">
-        <v>10.49478879948085</v>
+        <v>10.49467697559471</v>
       </c>
       <c r="N2" t="n">
-        <v>203.9467175982643</v>
+        <v>203.7550088358492</v>
       </c>
       <c r="O2" t="n">
-        <v>14.28099147812449</v>
+        <v>14.27427787440924</v>
       </c>
       <c r="P2" t="n">
-        <v>291.3497275513978</v>
+        <v>291.2874341192791</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21438,28 +21493,28 @@
         <v>0.1275</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6941496987142952</v>
+        <v>-0.6809359033513951</v>
       </c>
       <c r="J3" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09520386411021153</v>
+        <v>0.09196330381985651</v>
       </c>
       <c r="M3" t="n">
-        <v>12.79869788467499</v>
+        <v>12.81465627944681</v>
       </c>
       <c r="N3" t="n">
-        <v>265.7666537330449</v>
+        <v>266.6245949303157</v>
       </c>
       <c r="O3" t="n">
-        <v>16.3023511719336</v>
+        <v>16.32864338915869</v>
       </c>
       <c r="P3" t="n">
-        <v>269.1399071519007</v>
+        <v>269.0077026991561</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21516,28 +21571,28 @@
         <v>0.0459</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09428683562904674</v>
+        <v>-0.09007575225137003</v>
       </c>
       <c r="J4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005746484865563284</v>
+        <v>0.005269152420241396</v>
       </c>
       <c r="M4" t="n">
-        <v>7.334728365432973</v>
+        <v>7.336804130531608</v>
       </c>
       <c r="N4" t="n">
-        <v>87.61945352780046</v>
+        <v>87.54943165529762</v>
       </c>
       <c r="O4" t="n">
-        <v>9.360526348865243</v>
+        <v>9.356785326985847</v>
       </c>
       <c r="P4" t="n">
-        <v>246.5447656441248</v>
+        <v>246.5021955286635</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21594,28 +21649,28 @@
         <v>0.1024</v>
       </c>
       <c r="I5" t="n">
-        <v>0.364885365962921</v>
+        <v>0.3713034082139829</v>
       </c>
       <c r="J5" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K5" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0679177048065549</v>
+        <v>0.07031368021335604</v>
       </c>
       <c r="M5" t="n">
-        <v>8.243995102659092</v>
+        <v>8.260420408388882</v>
       </c>
       <c r="N5" t="n">
-        <v>104.0848931630465</v>
+        <v>104.1902771790377</v>
       </c>
       <c r="O5" t="n">
-        <v>10.20220040790449</v>
+        <v>10.20736387021829</v>
       </c>
       <c r="P5" t="n">
-        <v>239.2080096925494</v>
+        <v>239.1431292864499</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21672,28 +21727,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3513751097700155</v>
+        <v>-0.3513956673244155</v>
       </c>
       <c r="J6" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K6" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07929017353938239</v>
+        <v>0.0797438938897328</v>
       </c>
       <c r="M6" t="n">
-        <v>6.993343237149197</v>
+        <v>6.974591363406666</v>
       </c>
       <c r="N6" t="n">
-        <v>81.66744142119954</v>
+        <v>81.4473175063676</v>
       </c>
       <c r="O6" t="n">
-        <v>9.037004006926164</v>
+        <v>9.024816757495278</v>
       </c>
       <c r="P6" t="n">
-        <v>276.0243324943789</v>
+        <v>276.024540312032</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21750,28 +21805,28 @@
         <v>0.0809</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2991502382803918</v>
+        <v>-0.2943027894275527</v>
       </c>
       <c r="J7" t="n">
+        <v>373</v>
+      </c>
+      <c r="K7" t="n">
         <v>372</v>
       </c>
-      <c r="K7" t="n">
-        <v>371</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.08586832568145764</v>
+        <v>0.08349311961761441</v>
       </c>
       <c r="M7" t="n">
-        <v>5.69780130967524</v>
+        <v>5.704281888494286</v>
       </c>
       <c r="N7" t="n">
-        <v>54.12758817361141</v>
+        <v>54.20155190768146</v>
       </c>
       <c r="O7" t="n">
-        <v>7.357145382117402</v>
+        <v>7.362170325908078</v>
       </c>
       <c r="P7" t="n">
-        <v>292.7825544818798</v>
+        <v>292.7334968315863</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21828,28 +21883,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.27281493929818</v>
+        <v>-0.2681664408718647</v>
       </c>
       <c r="J8" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K8" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02295540889023395</v>
+        <v>0.0223048277148713</v>
       </c>
       <c r="M8" t="n">
-        <v>9.662050276463598</v>
+        <v>9.654054449300871</v>
       </c>
       <c r="N8" t="n">
-        <v>180.4295610722654</v>
+        <v>180.1457132129796</v>
       </c>
       <c r="O8" t="n">
-        <v>13.43240712129682</v>
+        <v>13.42183717726376</v>
       </c>
       <c r="P8" t="n">
-        <v>302.5399599362877</v>
+        <v>302.4929585176757</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21910,28 +21965,28 @@
         <v>0.1729</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4605548082075787</v>
+        <v>-0.4554576776548206</v>
       </c>
       <c r="J9" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K9" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04745749774383123</v>
+        <v>0.04668510519064495</v>
       </c>
       <c r="M9" t="n">
-        <v>11.25006842254031</v>
+        <v>11.23990247533903</v>
       </c>
       <c r="N9" t="n">
-        <v>244.2839168799159</v>
+        <v>243.871973126801</v>
       </c>
       <c r="O9" t="n">
-        <v>15.62958466754366</v>
+        <v>15.61640077376349</v>
       </c>
       <c r="P9" t="n">
-        <v>316.972922156354</v>
+        <v>316.9216115090724</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -21992,28 +22047,28 @@
         <v>0.1334</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5243185565234287</v>
+        <v>-0.5180473223278448</v>
       </c>
       <c r="J10" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K10" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07542034871761316</v>
+        <v>0.07404222453503195</v>
       </c>
       <c r="M10" t="n">
-        <v>10.55965895809293</v>
+        <v>10.55926769398252</v>
       </c>
       <c r="N10" t="n">
-        <v>193.0258238745831</v>
+        <v>192.879963667211</v>
       </c>
       <c r="O10" t="n">
-        <v>13.89337337994567</v>
+        <v>13.88812311535331</v>
       </c>
       <c r="P10" t="n">
-        <v>326.5211278191758</v>
+        <v>326.4580573791397</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22070,28 +22125,28 @@
         <v>0.1563</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.05315674314863816</v>
+        <v>-0.0497525180136832</v>
       </c>
       <c r="J11" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K11" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L11" t="n">
-        <v>0.000433488656697234</v>
+        <v>0.0003819609941262403</v>
       </c>
       <c r="M11" t="n">
-        <v>14.87438258164388</v>
+        <v>14.84697758261318</v>
       </c>
       <c r="N11" t="n">
-        <v>373.1812814933402</v>
+        <v>372.2903038923083</v>
       </c>
       <c r="O11" t="n">
-        <v>19.3179005456944</v>
+        <v>19.294825832132</v>
       </c>
       <c r="P11" t="n">
-        <v>322.461797167414</v>
+        <v>322.427560529051</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22148,28 +22203,28 @@
         <v>0.1938</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5145725610607494</v>
+        <v>0.5142665170104515</v>
       </c>
       <c r="J12" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K12" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0252894160287459</v>
+        <v>0.02541319772719963</v>
       </c>
       <c r="M12" t="n">
-        <v>18.62461289487549</v>
+        <v>18.5754887976488</v>
       </c>
       <c r="N12" t="n">
-        <v>573.1650900362072</v>
+        <v>571.5956233331054</v>
       </c>
       <c r="O12" t="n">
-        <v>23.9408665264273</v>
+        <v>23.90806607262715</v>
       </c>
       <c r="P12" t="n">
-        <v>309.946238873393</v>
+        <v>309.9493650293721</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22207,7 +22262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M373"/>
+  <dimension ref="A1:M374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47001,6 +47056,73 @@
         </is>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>-46.22071343894543,166.77810324550404</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>-46.22021283116478,166.77755486145048</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>-46.21965839325323,166.7770815868878</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-46.219308563616615,166.77632280150223</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>-46.21893829518058,166.77559253132267</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-46.21870642605582,166.77466913290047</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-46.218363804289304,166.77390027353752</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>-46.218022983604826,166.77312889573037</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>-46.21768035409859,166.77236003684177</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>-46.21729214648089,166.77165477482632</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>-46.21685578315217,166.77101670743988</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0520/nzd0520.xlsx
+++ b/data/nzd0520/nzd0520.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M374"/>
+  <dimension ref="A1:M377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17180,6 +17180,141 @@
       <c r="M374" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:29+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>294.58</v>
+      </c>
+      <c r="C375" t="n">
+        <v>284.34</v>
+      </c>
+      <c r="D375" t="n">
+        <v>260.97</v>
+      </c>
+      <c r="E375" t="n">
+        <v>270.8</v>
+      </c>
+      <c r="F375" t="n">
+        <v>271.66</v>
+      </c>
+      <c r="G375" t="n">
+        <v>298.84</v>
+      </c>
+      <c r="H375" t="n">
+        <v>311.83</v>
+      </c>
+      <c r="I375" t="n">
+        <v>321.52</v>
+      </c>
+      <c r="J375" t="n">
+        <v>329.78</v>
+      </c>
+      <c r="K375" t="n">
+        <v>332.45</v>
+      </c>
+      <c r="L375" t="n">
+        <v>327</v>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>299.66</v>
+      </c>
+      <c r="C376" t="n">
+        <v>279.02</v>
+      </c>
+      <c r="D376" t="n">
+        <v>263.84</v>
+      </c>
+      <c r="E376" t="n">
+        <v>277.22</v>
+      </c>
+      <c r="F376" t="n">
+        <v>272.38</v>
+      </c>
+      <c r="G376" t="n">
+        <v>302.88</v>
+      </c>
+      <c r="H376" t="n">
+        <v>309.8</v>
+      </c>
+      <c r="I376" t="n">
+        <v>316.18</v>
+      </c>
+      <c r="J376" t="n">
+        <v>326.91</v>
+      </c>
+      <c r="K376" t="n">
+        <v>325.69</v>
+      </c>
+      <c r="L376" t="n">
+        <v>318.65</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:32:28+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>298.23</v>
+      </c>
+      <c r="C377" t="n">
+        <v>274.2</v>
+      </c>
+      <c r="D377" t="n">
+        <v>260.23</v>
+      </c>
+      <c r="E377" t="n">
+        <v>273.99</v>
+      </c>
+      <c r="F377" t="n">
+        <v>271.93</v>
+      </c>
+      <c r="G377" t="n">
+        <v>300.33</v>
+      </c>
+      <c r="H377" t="n">
+        <v>305.76</v>
+      </c>
+      <c r="I377" t="n">
+        <v>308.25</v>
+      </c>
+      <c r="J377" t="n">
+        <v>319.13</v>
+      </c>
+      <c r="K377" t="n">
+        <v>317.9</v>
+      </c>
+      <c r="L377" t="n">
+        <v>309.51</v>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B405"/>
+  <dimension ref="A1:B408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21247,6 +21382,36 @@
       </c>
       <c r="B405" t="n">
         <v>0.53</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>-0.86</v>
       </c>
     </row>
   </sheetData>
@@ -21415,28 +21580,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5173794221230359</v>
+        <v>-0.4859050702389542</v>
       </c>
       <c r="J2" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K2" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07122927031148285</v>
+        <v>0.06349251077713491</v>
       </c>
       <c r="M2" t="n">
-        <v>10.49467697559471</v>
+        <v>10.55557286942964</v>
       </c>
       <c r="N2" t="n">
-        <v>203.7550088358492</v>
+        <v>205.3117451116833</v>
       </c>
       <c r="O2" t="n">
-        <v>14.27427787440924</v>
+        <v>14.32870353910929</v>
       </c>
       <c r="P2" t="n">
-        <v>291.2874341192791</v>
+        <v>290.9694647400113</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21493,28 +21658,28 @@
         <v>0.1275</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6809359033513951</v>
+        <v>-0.6348246881715714</v>
       </c>
       <c r="J3" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K3" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09196330381985651</v>
+        <v>0.08044444844285248</v>
       </c>
       <c r="M3" t="n">
-        <v>12.81465627944681</v>
+        <v>12.89386240806707</v>
       </c>
       <c r="N3" t="n">
-        <v>266.6245949303157</v>
+        <v>271.0903245099727</v>
       </c>
       <c r="O3" t="n">
-        <v>16.32864338915869</v>
+        <v>16.46482081621214</v>
       </c>
       <c r="P3" t="n">
-        <v>269.0077026991561</v>
+        <v>268.5436217801337</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21571,28 +21736,28 @@
         <v>0.0459</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09007575225137003</v>
+        <v>-0.06231428061561167</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K4" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005269152420241396</v>
+        <v>0.002505182652497551</v>
       </c>
       <c r="M4" t="n">
-        <v>7.336804130531608</v>
+        <v>7.420609609152086</v>
       </c>
       <c r="N4" t="n">
-        <v>87.54943165529762</v>
+        <v>89.28026703504946</v>
       </c>
       <c r="O4" t="n">
-        <v>9.356785326985847</v>
+        <v>9.448823579422438</v>
       </c>
       <c r="P4" t="n">
-        <v>246.5021955286635</v>
+        <v>246.2198637862381</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21649,28 +21814,28 @@
         <v>0.1024</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3713034082139829</v>
+        <v>0.4107619217642271</v>
       </c>
       <c r="J5" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K5" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07031368021335604</v>
+        <v>0.08254885197967032</v>
       </c>
       <c r="M5" t="n">
-        <v>8.260420408388882</v>
+        <v>8.431287234197354</v>
       </c>
       <c r="N5" t="n">
-        <v>104.1902771790377</v>
+        <v>108.2832598535496</v>
       </c>
       <c r="O5" t="n">
-        <v>10.20736387021829</v>
+        <v>10.40592426714464</v>
       </c>
       <c r="P5" t="n">
-        <v>239.1431292864499</v>
+        <v>238.7417969714095</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21727,28 +21892,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3513956673244155</v>
+        <v>-0.3429929184946538</v>
       </c>
       <c r="J6" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K6" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0797438938897328</v>
+        <v>0.0773641479253353</v>
       </c>
       <c r="M6" t="n">
-        <v>6.974591363406666</v>
+        <v>6.963059697841562</v>
       </c>
       <c r="N6" t="n">
-        <v>81.4473175063676</v>
+        <v>81.01584089116363</v>
       </c>
       <c r="O6" t="n">
-        <v>9.024816757495278</v>
+        <v>9.000880006486234</v>
       </c>
       <c r="P6" t="n">
-        <v>276.024540312032</v>
+        <v>275.939081273916</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21805,28 +21970,28 @@
         <v>0.0809</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2943027894275527</v>
+        <v>-0.2693621495243615</v>
       </c>
       <c r="J7" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K7" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08349311961761441</v>
+        <v>0.06975216208842261</v>
       </c>
       <c r="M7" t="n">
-        <v>5.704281888494286</v>
+        <v>5.769448900181104</v>
       </c>
       <c r="N7" t="n">
-        <v>54.20155190768146</v>
+        <v>55.73167457673656</v>
       </c>
       <c r="O7" t="n">
-        <v>7.362170325908078</v>
+        <v>7.465364999565431</v>
       </c>
       <c r="P7" t="n">
-        <v>292.7334968315863</v>
+        <v>292.4795542467927</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21883,28 +22048,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2681664408718647</v>
+        <v>-0.2464242458274965</v>
       </c>
       <c r="J8" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K8" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0223048277148713</v>
+        <v>0.01908132184658384</v>
       </c>
       <c r="M8" t="n">
-        <v>9.654054449300871</v>
+        <v>9.662305101675249</v>
       </c>
       <c r="N8" t="n">
-        <v>180.1457132129796</v>
+        <v>180.2337548430918</v>
       </c>
       <c r="O8" t="n">
-        <v>13.42183717726376</v>
+        <v>13.42511656720685</v>
       </c>
       <c r="P8" t="n">
-        <v>302.4929585176757</v>
+        <v>302.2718579934901</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21965,28 +22130,28 @@
         <v>0.1729</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4554576776548206</v>
+        <v>-0.4389694499826695</v>
       </c>
       <c r="J9" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K9" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04668510519064495</v>
+        <v>0.04408127702697051</v>
       </c>
       <c r="M9" t="n">
-        <v>11.23990247533903</v>
+        <v>11.21591870702746</v>
       </c>
       <c r="N9" t="n">
-        <v>243.871973126801</v>
+        <v>243.0175392993903</v>
       </c>
       <c r="O9" t="n">
-        <v>15.61640077376349</v>
+        <v>15.58901983125913</v>
       </c>
       <c r="P9" t="n">
-        <v>316.9216115090724</v>
+        <v>316.754752696228</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22047,28 +22212,28 @@
         <v>0.1334</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5180473223278448</v>
+        <v>-0.498295935558017</v>
       </c>
       <c r="J10" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K10" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07404222453503195</v>
+        <v>0.06959098815993614</v>
       </c>
       <c r="M10" t="n">
-        <v>10.55926769398252</v>
+        <v>10.56240185612048</v>
       </c>
       <c r="N10" t="n">
-        <v>192.879963667211</v>
+        <v>192.7360031716492</v>
       </c>
       <c r="O10" t="n">
-        <v>13.88812311535331</v>
+        <v>13.88293928430321</v>
       </c>
       <c r="P10" t="n">
-        <v>326.4580573791397</v>
+        <v>326.2583157300534</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22125,28 +22290,28 @@
         <v>0.1563</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0497525180136832</v>
+        <v>-0.04312426895092123</v>
       </c>
       <c r="J11" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K11" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003819609941262403</v>
+        <v>0.0002919346224491415</v>
       </c>
       <c r="M11" t="n">
-        <v>14.84697758261318</v>
+        <v>14.77001061016384</v>
       </c>
       <c r="N11" t="n">
-        <v>372.2903038923083</v>
+        <v>369.7416185050744</v>
       </c>
       <c r="O11" t="n">
-        <v>19.294825832132</v>
+        <v>19.22866658156707</v>
       </c>
       <c r="P11" t="n">
-        <v>322.427560529051</v>
+        <v>322.3606401779741</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22203,28 +22368,28 @@
         <v>0.1938</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5142665170104515</v>
+        <v>0.5057294017107751</v>
       </c>
       <c r="J12" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K12" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02541319772719963</v>
+        <v>0.02502037480235542</v>
       </c>
       <c r="M12" t="n">
-        <v>18.5754887976488</v>
+        <v>18.49496501791561</v>
       </c>
       <c r="N12" t="n">
-        <v>571.5956233331054</v>
+        <v>567.572715077389</v>
       </c>
       <c r="O12" t="n">
-        <v>23.90806607262715</v>
+        <v>23.82378465058373</v>
       </c>
       <c r="P12" t="n">
-        <v>309.9493650293721</v>
+        <v>310.0372631942655</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22262,7 +22427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M374"/>
+  <dimension ref="A1:M377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47123,6 +47288,207 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:29+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>-46.22074850798349,166.7780543105289</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>-46.22027491083494,166.77746823621817</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>-46.21971666932878,166.77700026955824</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-46.21937244767255,166.77623365830405</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-46.21897039816918,166.7755477349183</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-46.218738013040976,166.77462505594391</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-46.218414149709645,166.77383002025013</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>-46.218069009693906,166.77306466930185</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>-46.21771464780819,166.7723121818717</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>-46.21732424828925,166.7716099783384</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>-46.21688150314264,166.77098081640946</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-46.22078125625444,166.778008613841</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>-46.2202406155333,166.77751609151102</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-46.21973517067946,166.77697445306893</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-46.21941383366779,166.77617590851244</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-46.21897503956343,166.77554125832532</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-46.2187640561731,166.7745887149047</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>-46.21840106377294,166.7738482807201</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>-46.21803458682453,166.77311270420395</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>-46.21769614725721,166.77233799837617</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>-46.217280672335605,166.7716707864096</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>-46.21682767808501,166.77105592667263</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:32:28+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>-46.22077203774724,166.77802147728426</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>-46.22020954345425,166.77755944907412</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>-46.219711898944595,166.77700692607183</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-46.219393011746085,166.77620496332506</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-46.21897213869207,166.77554530619605</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-46.218747618059076,166.7746116529409</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>-46.21837502081494,166.77388462172797</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>-46.21798346817568,166.77318403682148</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>-46.217645995903844,166.77240798170453</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>-46.21723045680409,166.77174085949562</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>-46.21676876053124,166.77113814300665</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
